--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260805.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>202608WTX</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>115/08台股期貨</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>9,852,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.90%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202608WTX</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>115/08台股期貨</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>9,852,000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.85%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>46,121,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5,972,000</t>
+          <t>46,121,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -726,139 +726,139 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>20,089,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,587,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>30,079,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>25,898,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -1012,200 +1012,200 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>3,104,872,569</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,169,000</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,929,621,425</t>
+          <t>2,169,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>9,174,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,904,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,105 +1217,105 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>2,481,625,322</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,338,465,322</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,44 +1349,44 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>3,498,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>3,498,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1474,51 +1474,51 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>8,951,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>8,951,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1562,46 +1562,46 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1657,83 +1657,83 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>18,174,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>18,174,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-11,181,870</t>
+          <t>-6,727,758</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
